--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VersioningAttributes/outputfile.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VersioningAttributes/outputfile.xlsx
@@ -32,637 +32,637 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
+    <x:t>Age</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FullName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gwendolyn Holstein</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Female</x:t>
+  </x:si>
+  <x:si>
+    <x:t>202.45.194.182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vivia Ferne</x:t>
+  </x:si>
+  <x:si>
+    <x:t>204.111.177.99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Robby Zecchi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>178.181.18.15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Katti Riteley</x:t>
+  </x:si>
+  <x:si>
+    <x:t>82.55.9.224</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dita Uzzell</x:t>
+  </x:si>
+  <x:si>
+    <x:t>195.91.193.170</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dunstan Jandl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Male</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.97.68.208</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pepito Gibard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.139.200.5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dominik Abby</x:t>
+  </x:si>
+  <x:si>
+    <x:t>91.116.137.203</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vinnie Boarer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>193.21.180.180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Erich Crittal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>168.240.154.238</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Al Bullion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>62.99.152.149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Granny Eger</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.157.156.125</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cheri Sirmon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>146.69.50.129</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vasily De Caroli</x:t>
+  </x:si>
+  <x:si>
+    <x:t>203.237.164.29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Em Tooley</x:t>
+  </x:si>
+  <x:si>
+    <x:t>53.98.54.229</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Elora Peyzer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>152.250.34.201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pennie Cocci</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.241.106.176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Zerk Geeves</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.37.110.206</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Izzy Mellsop</x:t>
+  </x:si>
+  <x:si>
+    <x:t>227.208.97.133</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Zacherie Tofano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>204.115.95.235</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Savina Blest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>185.222.202.35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tremaine Mailey</x:t>
+  </x:si>
+  <x:si>
+    <x:t>163.187.30.249</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cherish Blowin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>54.164.124.167</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thaddeus Berrick</x:t>
+  </x:si>
+  <x:si>
+    <x:t>92.181.37.212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mason Guilliland</x:t>
+  </x:si>
+  <x:si>
+    <x:t>201.248.191.217</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Staffard Marvelley</x:t>
+  </x:si>
+  <x:si>
+    <x:t>233.108.60.107</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Artur Stroud</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.0.114.250</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kirk Balwin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>106.0.247.243</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Solomon Patinkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>145.25.14.10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Fernande Frape</x:t>
+  </x:si>
+  <x:si>
+    <x:t>63.19.148.247</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Otha Pragnall</x:t>
+  </x:si>
+  <x:si>
+    <x:t>143.158.51.93</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sidonia Cursons</x:t>
+  </x:si>
+  <x:si>
+    <x:t>247.60.229.19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Farlay Churchill</x:t>
+  </x:si>
+  <x:si>
+    <x:t>50.243.139.233</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mikol Payfoot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>173.246.93.121</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Shandra Coad</x:t>
+  </x:si>
+  <x:si>
+    <x:t>219.82.159.40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Muffin Symmers</x:t>
+  </x:si>
+  <x:si>
+    <x:t>135.185.34.151</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Norbert Simkins</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45.242.82.200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dionisio Brimilcombe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>93.139.211.99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Isac Bestwick</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36.121.179.186</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Troy Edlin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>244.175.137.119</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Massimo Ricard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>240.12.55.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bryce Guillard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>101.111.129.162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Robena Petris</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33.132.202.203</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Abe Moiser</x:t>
+  </x:si>
+  <x:si>
+    <x:t>158.223.145.79</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Iosep Skellorne</x:t>
+  </x:si>
+  <x:si>
+    <x:t>228.223.123.75</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Idaline Innman</x:t>
+  </x:si>
+  <x:si>
+    <x:t>247.168.146.19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cello Ticksall</x:t>
+  </x:si>
+  <x:si>
+    <x:t>73.147.212.62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rafaello Hampshaw</x:t>
+  </x:si>
+  <x:si>
+    <x:t>224.166.105.222</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sherm McCuaig</x:t>
+  </x:si>
+  <x:si>
+    <x:t>104.211.158.194</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Jory Finch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35.22.51.254</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Peterus Horsey</x:t>
+  </x:si>
+  <x:si>
+    <x:t>220.181.157.99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mylo Collum</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.9.154.12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Oran Brimilcombe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>203.240.48.149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Winona Cawcutt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>248.140.174.102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Eileen De Laspee</x:t>
+  </x:si>
+  <x:si>
+    <x:t>112.211.240.245</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sheila-kathryn Bent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>125.214.233.201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nelia Dudley</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.158.128.230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ulysses Hunte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>164.143.147.20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kyla McAnulty</x:t>
+  </x:si>
+  <x:si>
+    <x:t>255.86.133.18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bil Eunson</x:t>
+  </x:si>
+  <x:si>
+    <x:t>102.142.43.172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cora Kenlin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.203.122.183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Beverly Winspur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>64.104.110.115</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hobard Castillon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>210.81.217.85</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sam Gilligan</x:t>
+  </x:si>
+  <x:si>
+    <x:t>178.193.63.53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trev MacMakin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>230.192.12.25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kylila Bache</x:t>
+  </x:si>
+  <x:si>
+    <x:t>172.214.218.255</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Elwood Furmagier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33.151.238.228</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Conrad Perri</x:t>
+  </x:si>
+  <x:si>
+    <x:t>102.88.99.96</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Linea Berthot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.21.6.255</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Costanza Dungay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>234.186.52.64</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Imojean Yve</x:t>
+  </x:si>
+  <x:si>
+    <x:t>205.22.49.211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cherye Delve</x:t>
+  </x:si>
+  <x:si>
+    <x:t>89.17.9.203</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Saw O'Grada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>214.15.241.95</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Angelia Glendza</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26.156.14.132</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Roze Foulds</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.102.55.28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Adair Allsobrook</x:t>
+  </x:si>
+  <x:si>
+    <x:t>200.169.227.85</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dalli Mallebone</x:t>
+  </x:si>
+  <x:si>
+    <x:t>75.36.125.212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Giacinta Lusk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>133.48.225.108</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lauren Abrahmer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>139.126.222.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Jakie Murley</x:t>
+  </x:si>
+  <x:si>
+    <x:t>78.135.64.43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Franny Bartoszewicz</x:t>
+  </x:si>
+  <x:si>
+    <x:t>105.189.69.205</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sullivan Hallaways</x:t>
+  </x:si>
+  <x:si>
+    <x:t>217.100.47.134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Borden Shane</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.98.124.169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ariela Lichfield</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.9.5.111</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ianthe Ronaldson</x:t>
+  </x:si>
+  <x:si>
+    <x:t>127.199.7.104</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renado Oaker</x:t>
+  </x:si>
+  <x:si>
+    <x:t>247.255.250.93</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Marty Brezlaw</x:t>
+  </x:si>
+  <x:si>
+    <x:t>238.5.0.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lorry Cudd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>58.7.202.165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Brigham Draisey</x:t>
+  </x:si>
+  <x:si>
+    <x:t>245.215.45.165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Corbett Caskie</x:t>
+  </x:si>
+  <x:si>
+    <x:t>252.140.216.249</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Egbert Errichi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.237.50.211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kathleen Shakesby</x:t>
+  </x:si>
+  <x:si>
+    <x:t>44.247.91.77</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Jacinthe Mulchrone</x:t>
+  </x:si>
+  <x:si>
+    <x:t>132.148.93.151</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ermanno Pifford</x:t>
+  </x:si>
+  <x:si>
+    <x:t>122.87.178.124</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nonie Calvard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>97.240.228.116</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Curcio Godon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>218.101.77.119</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Winni Annis</x:t>
+  </x:si>
+  <x:si>
+    <x:t>79.13.213.88</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Micheil Kiehnlt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.28.148.212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Chad Sopp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.219.115.172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Emera Clawsley</x:t>
+  </x:si>
+  <x:si>
+    <x:t>232.193.153.155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sex</x:t>
+  </x:si>
+  <x:si>
     <x:t>IPAddress</x:t>
   </x:si>
   <x:si>
+    <x:t>Row Labels</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grand Total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Average of Age</x:t>
+  </x:si>
+  <x:si>
     <x:t>(All)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Row Labels</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Average of Age</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Female</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Male</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grand Total</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FullName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Age</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sex</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gwendolyn Holstein</x:t>
-  </x:si>
-  <x:si>
-    <x:t>202.45.194.182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Vivia Ferne</x:t>
-  </x:si>
-  <x:si>
-    <x:t>204.111.177.99</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Robby Zecchi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>178.181.18.15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Katti Riteley</x:t>
-  </x:si>
-  <x:si>
-    <x:t>82.55.9.224</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dita Uzzell</x:t>
-  </x:si>
-  <x:si>
-    <x:t>195.91.193.170</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dunstan Jandl</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.97.68.208</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pepito Gibard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.139.200.5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dominik Abby</x:t>
-  </x:si>
-  <x:si>
-    <x:t>91.116.137.203</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Vinnie Boarer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>193.21.180.180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Erich Crittal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>168.240.154.238</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Al Bullion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>62.99.152.149</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Granny Eger</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.157.156.125</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cheri Sirmon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>146.69.50.129</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Vasily De Caroli</x:t>
-  </x:si>
-  <x:si>
-    <x:t>203.237.164.29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Em Tooley</x:t>
-  </x:si>
-  <x:si>
-    <x:t>53.98.54.229</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Elora Peyzer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>152.250.34.201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pennie Cocci</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.241.106.176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Zerk Geeves</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.37.110.206</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Izzy Mellsop</x:t>
-  </x:si>
-  <x:si>
-    <x:t>227.208.97.133</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Zacherie Tofano</x:t>
-  </x:si>
-  <x:si>
-    <x:t>204.115.95.235</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Savina Blest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>185.222.202.35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tremaine Mailey</x:t>
-  </x:si>
-  <x:si>
-    <x:t>163.187.30.249</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cherish Blowin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>54.164.124.167</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Thaddeus Berrick</x:t>
-  </x:si>
-  <x:si>
-    <x:t>92.181.37.212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mason Guilliland</x:t>
-  </x:si>
-  <x:si>
-    <x:t>201.248.191.217</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Staffard Marvelley</x:t>
-  </x:si>
-  <x:si>
-    <x:t>233.108.60.107</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Artur Stroud</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.0.114.250</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kirk Balwin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>106.0.247.243</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Solomon Patinkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>145.25.14.10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Fernande Frape</x:t>
-  </x:si>
-  <x:si>
-    <x:t>63.19.148.247</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Otha Pragnall</x:t>
-  </x:si>
-  <x:si>
-    <x:t>143.158.51.93</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sidonia Cursons</x:t>
-  </x:si>
-  <x:si>
-    <x:t>247.60.229.19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Farlay Churchill</x:t>
-  </x:si>
-  <x:si>
-    <x:t>50.243.139.233</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mikol Payfoot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>173.246.93.121</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Shandra Coad</x:t>
-  </x:si>
-  <x:si>
-    <x:t>219.82.159.40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Muffin Symmers</x:t>
-  </x:si>
-  <x:si>
-    <x:t>135.185.34.151</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Norbert Simkins</x:t>
-  </x:si>
-  <x:si>
-    <x:t>45.242.82.200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dionisio Brimilcombe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>93.139.211.99</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Isac Bestwick</x:t>
-  </x:si>
-  <x:si>
-    <x:t>36.121.179.186</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Troy Edlin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>244.175.137.119</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Massimo Ricard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>240.12.55.3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bryce Guillard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>101.111.129.162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Robena Petris</x:t>
-  </x:si>
-  <x:si>
-    <x:t>33.132.202.203</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Abe Moiser</x:t>
-  </x:si>
-  <x:si>
-    <x:t>158.223.145.79</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Iosep Skellorne</x:t>
-  </x:si>
-  <x:si>
-    <x:t>228.223.123.75</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Idaline Innman</x:t>
-  </x:si>
-  <x:si>
-    <x:t>247.168.146.19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cello Ticksall</x:t>
-  </x:si>
-  <x:si>
-    <x:t>73.147.212.62</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rafaello Hampshaw</x:t>
-  </x:si>
-  <x:si>
-    <x:t>224.166.105.222</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sherm McCuaig</x:t>
-  </x:si>
-  <x:si>
-    <x:t>104.211.158.194</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Jory Finch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35.22.51.254</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Peterus Horsey</x:t>
-  </x:si>
-  <x:si>
-    <x:t>220.181.157.99</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mylo Collum</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.9.154.12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Oran Brimilcombe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>203.240.48.149</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Winona Cawcutt</x:t>
-  </x:si>
-  <x:si>
-    <x:t>248.140.174.102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Eileen De Laspee</x:t>
-  </x:si>
-  <x:si>
-    <x:t>112.211.240.245</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sheila-kathryn Bent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>125.214.233.201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nelia Dudley</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.158.128.230</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ulysses Hunte</x:t>
-  </x:si>
-  <x:si>
-    <x:t>164.143.147.20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kyla McAnulty</x:t>
-  </x:si>
-  <x:si>
-    <x:t>255.86.133.18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bil Eunson</x:t>
-  </x:si>
-  <x:si>
-    <x:t>102.142.43.172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cora Kenlin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.203.122.183</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Beverly Winspur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>64.104.110.115</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hobard Castillon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>210.81.217.85</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sam Gilligan</x:t>
-  </x:si>
-  <x:si>
-    <x:t>178.193.63.53</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Trev MacMakin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>230.192.12.25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kylila Bache</x:t>
-  </x:si>
-  <x:si>
-    <x:t>172.214.218.255</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Elwood Furmagier</x:t>
-  </x:si>
-  <x:si>
-    <x:t>33.151.238.228</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Conrad Perri</x:t>
-  </x:si>
-  <x:si>
-    <x:t>102.88.99.96</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Linea Berthot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.21.6.255</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Costanza Dungay</x:t>
-  </x:si>
-  <x:si>
-    <x:t>234.186.52.64</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Imojean Yve</x:t>
-  </x:si>
-  <x:si>
-    <x:t>205.22.49.211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cherye Delve</x:t>
-  </x:si>
-  <x:si>
-    <x:t>89.17.9.203</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Saw O'Grada</x:t>
-  </x:si>
-  <x:si>
-    <x:t>214.15.241.95</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Angelia Glendza</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.156.14.132</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Roze Foulds</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.102.55.28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Adair Allsobrook</x:t>
-  </x:si>
-  <x:si>
-    <x:t>200.169.227.85</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dalli Mallebone</x:t>
-  </x:si>
-  <x:si>
-    <x:t>75.36.125.212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Giacinta Lusk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>133.48.225.108</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lauren Abrahmer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>139.126.222.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Jakie Murley</x:t>
-  </x:si>
-  <x:si>
-    <x:t>78.135.64.43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Franny Bartoszewicz</x:t>
-  </x:si>
-  <x:si>
-    <x:t>105.189.69.205</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sullivan Hallaways</x:t>
-  </x:si>
-  <x:si>
-    <x:t>217.100.47.134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Borden Shane</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.98.124.169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ariela Lichfield</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.9.5.111</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ianthe Ronaldson</x:t>
-  </x:si>
-  <x:si>
-    <x:t>127.199.7.104</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Renado Oaker</x:t>
-  </x:si>
-  <x:si>
-    <x:t>247.255.250.93</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Marty Brezlaw</x:t>
-  </x:si>
-  <x:si>
-    <x:t>238.5.0.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lorry Cudd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>58.7.202.165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Brigham Draisey</x:t>
-  </x:si>
-  <x:si>
-    <x:t>245.215.45.165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Corbett Caskie</x:t>
-  </x:si>
-  <x:si>
-    <x:t>252.140.216.249</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Egbert Errichi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.237.50.211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kathleen Shakesby</x:t>
-  </x:si>
-  <x:si>
-    <x:t>44.247.91.77</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Jacinthe Mulchrone</x:t>
-  </x:si>
-  <x:si>
-    <x:t>132.148.93.151</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ermanno Pifford</x:t>
-  </x:si>
-  <x:si>
-    <x:t>122.87.178.124</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nonie Calvard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>97.240.228.116</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Curcio Godon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>218.101.77.119</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Winni Annis</x:t>
-  </x:si>
-  <x:si>
-    <x:t>79.13.213.88</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Micheil Kiehnlt</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.28.148.212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Chad Sopp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.219.115.172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Emera Clawsley</x:t>
-  </x:si>
-  <x:si>
-    <x:t>232.193.153.155</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2248,18 +2248,18 @@
   <x:sheetData>
     <x:row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <x:c r="A1" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>1</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <x:c r="A3" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>209</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2272,7 +2272,7 @@
     </x:row>
     <x:row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <x:c r="A5" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B5" s="0">
         <x:v>61.4912280701754</x:v>
@@ -2280,7 +2280,7 @@
     </x:row>
     <x:row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <x:c r="A6" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B6" s="0">
         <x:v>61.23</x:v>
@@ -2312,19 +2312,19 @@
   <x:sheetData>
     <x:row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <x:c r="A1" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -2332,7 +2332,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>99</x:v>
@@ -2341,7 +2341,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2349,7 +2349,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C3" s="0">
         <x:v>58</x:v>
@@ -2358,7 +2358,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2366,7 +2366,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>38</x:v>
@@ -2375,7 +2375,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2383,7 +2383,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C5" s="0">
         <x:v>98</x:v>
@@ -2392,7 +2392,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -2400,7 +2400,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C6" s="0">
         <x:v>64</x:v>
@@ -2409,7 +2409,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2417,16 +2417,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>33</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2434,16 +2434,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0">
         <x:v>31</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2451,16 +2451,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C9" s="0">
         <x:v>64</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2468,7 +2468,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C10" s="0">
         <x:v>46</x:v>
@@ -2477,7 +2477,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2485,16 +2485,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="0">
         <x:v>63</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2502,16 +2502,16 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C12" s="0">
         <x:v>95</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2519,16 +2519,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C13" s="0">
         <x:v>90</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2536,7 +2536,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C14" s="0">
         <x:v>51</x:v>
@@ -2545,7 +2545,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2553,16 +2553,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C15" s="0">
         <x:v>82</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2570,7 +2570,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C16" s="0">
         <x:v>88</x:v>
@@ -2579,7 +2579,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -2587,7 +2587,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C17" s="0">
         <x:v>34</x:v>
@@ -2596,7 +2596,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -2604,7 +2604,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C18" s="0">
         <x:v>79</x:v>
@@ -2613,7 +2613,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -2621,16 +2621,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C19" s="0">
         <x:v>84</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -2638,16 +2638,16 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C20" s="0">
         <x:v>51</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -2655,16 +2655,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C21" s="0">
         <x:v>40</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -2672,7 +2672,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C22" s="0">
         <x:v>48</x:v>
@@ -2681,7 +2681,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -2689,16 +2689,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C23" s="0">
         <x:v>49</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -2706,7 +2706,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C24" s="0">
         <x:v>82</x:v>
@@ -2715,7 +2715,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -2723,16 +2723,16 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C25" s="0">
         <x:v>83</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -2740,16 +2740,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C26" s="0">
         <x:v>71</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -2757,16 +2757,16 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C27" s="0">
         <x:v>91</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -2774,16 +2774,16 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C28" s="0">
         <x:v>88</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2791,16 +2791,16 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C29" s="0">
         <x:v>81</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -2808,16 +2808,16 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C30" s="0">
         <x:v>87</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -2825,7 +2825,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C31" s="0">
         <x:v>26</x:v>
@@ -2834,7 +2834,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -2842,7 +2842,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C32" s="0">
         <x:v>45</x:v>
@@ -2851,7 +2851,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2859,7 +2859,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C33" s="0">
         <x:v>66</x:v>
@@ -2868,7 +2868,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2876,16 +2876,16 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C34" s="0">
         <x:v>67</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -2893,16 +2893,16 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C35" s="0">
         <x:v>94</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -2910,7 +2910,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C36" s="0">
         <x:v>43</x:v>
@@ -2919,7 +2919,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2927,16 +2927,16 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C37" s="0">
         <x:v>71</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -2944,16 +2944,16 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C38" s="0">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2961,16 +2961,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C39" s="0">
         <x:v>99</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -2978,16 +2978,16 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C40" s="0">
         <x:v>64</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2995,16 +2995,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C41" s="0">
         <x:v>60</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3012,16 +3012,16 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C42" s="0">
         <x:v>69</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -3029,16 +3029,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C43" s="0">
         <x:v>46</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -3046,7 +3046,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C44" s="0">
         <x:v>81</x:v>
@@ -3055,7 +3055,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -3063,16 +3063,16 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C45" s="0">
         <x:v>80</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -3080,16 +3080,16 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C46" s="0">
         <x:v>51</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -3097,7 +3097,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C47" s="0">
         <x:v>65</x:v>
@@ -3106,7 +3106,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3114,16 +3114,16 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C48" s="0">
         <x:v>36</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3131,16 +3131,16 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C49" s="0">
         <x:v>31</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -3148,16 +3148,16 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C50" s="0">
         <x:v>58</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -3165,16 +3165,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C51" s="0">
         <x:v>30</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -3182,16 +3182,16 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C52" s="0">
         <x:v>75</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -3199,16 +3199,16 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C53" s="0">
         <x:v>45</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -3216,16 +3216,16 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C54" s="0">
         <x:v>43</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -3233,7 +3233,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C55" s="0">
         <x:v>44</x:v>
@@ -3242,7 +3242,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -3250,7 +3250,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C56" s="0">
         <x:v>52</x:v>
@@ -3259,7 +3259,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -3267,7 +3267,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C57" s="0">
         <x:v>100</x:v>
@@ -3276,7 +3276,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -3284,7 +3284,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C58" s="0">
         <x:v>59</x:v>
@@ -3293,7 +3293,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -3301,16 +3301,16 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C59" s="0">
         <x:v>40</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -3318,7 +3318,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C60" s="0">
         <x:v>53</x:v>
@@ -3327,7 +3327,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -3335,16 +3335,16 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C61" s="0">
         <x:v>31</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3352,7 +3352,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C62" s="0">
         <x:v>63</x:v>
@@ -3361,7 +3361,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -3369,7 +3369,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C63" s="0">
         <x:v>34</x:v>
@@ -3378,7 +3378,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -3386,16 +3386,16 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C64" s="0">
         <x:v>65</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -3403,16 +3403,16 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C65" s="0">
         <x:v>67</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -3420,16 +3420,16 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C66" s="0">
         <x:v>35</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -3437,7 +3437,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C67" s="0">
         <x:v>81</x:v>
@@ -3446,7 +3446,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -3454,16 +3454,16 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C68" s="0">
         <x:v>30</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -3471,16 +3471,16 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C69" s="0">
         <x:v>92</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -3488,7 +3488,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C70" s="0">
         <x:v>37</x:v>
@@ -3497,7 +3497,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3505,7 +3505,7 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C71" s="0">
         <x:v>43</x:v>
@@ -3514,7 +3514,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3522,7 +3522,7 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C72" s="0">
         <x:v>41</x:v>
@@ -3531,7 +3531,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3539,7 +3539,7 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C73" s="0">
         <x:v>45</x:v>
@@ -3548,7 +3548,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3556,16 +3556,16 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C74" s="0">
         <x:v>92</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3573,7 +3573,7 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C75" s="0">
         <x:v>24</x:v>
@@ -3582,7 +3582,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -3590,7 +3590,7 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C76" s="0">
         <x:v>44</x:v>
@@ -3599,7 +3599,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -3607,16 +3607,16 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C77" s="0">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -3624,16 +3624,16 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C78" s="0">
         <x:v>96</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -3641,7 +3641,7 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C79" s="0">
         <x:v>71</x:v>
@@ -3650,7 +3650,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -3658,7 +3658,7 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C80" s="0">
         <x:v>39</x:v>
@@ -3667,7 +3667,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -3675,16 +3675,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C81" s="0">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -3692,7 +3692,7 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C82" s="0">
         <x:v>67</x:v>
@@ -3701,7 +3701,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>166</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -3709,16 +3709,16 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C83" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -3726,16 +3726,16 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C84" s="0">
         <x:v>43</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -3743,7 +3743,7 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C85" s="0">
         <x:v>90</x:v>
@@ -3752,7 +3752,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -3760,7 +3760,7 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C86" s="0">
         <x:v>49</x:v>
@@ -3769,7 +3769,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -3777,16 +3777,16 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C87" s="0">
         <x:v>47</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -3794,16 +3794,16 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C88" s="0">
         <x:v>82</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -3811,16 +3811,16 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C89" s="0">
         <x:v>95</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -3828,16 +3828,16 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C90" s="0">
         <x:v>47</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -3845,16 +3845,16 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C91" s="0">
         <x:v>47</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -3862,16 +3862,16 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C92" s="0">
         <x:v>70</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -3879,7 +3879,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C93" s="0">
         <x:v>81</x:v>
@@ -3888,7 +3888,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>188</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -3896,7 +3896,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C94" s="0">
         <x:v>94</x:v>
@@ -3905,7 +3905,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -3913,16 +3913,16 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C95" s="0">
         <x:v>57</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -3930,7 +3930,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C96" s="0">
         <x:v>82</x:v>
@@ -3939,7 +3939,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -3947,16 +3947,16 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C97" s="0">
         <x:v>33</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -3964,7 +3964,7 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C98" s="0">
         <x:v>99</x:v>
@@ -3973,7 +3973,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -3981,16 +3981,16 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C99" s="0">
         <x:v>54</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -3998,7 +3998,7 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C100" s="0">
         <x:v>69</x:v>
@@ -4007,7 +4007,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -4015,7 +4015,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C101" s="0">
         <x:v>46</x:v>
@@ -4024,7 +4024,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VersioningAttributes/outputfile.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VersioningAttributes/outputfile.xlsx
@@ -2309,1725 +2309,1725 @@
     <x:col min="4" max="4" width="7.570312" style="0" bestFit="1" customWidth="1"/>
     <x:col min="5" max="5" width="14.855469" style="0" bestFit="1" customWidth="1"/>
   </x:cols>
-  <x:sheetData>
-    <x:row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A1" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B1" s="1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C1" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D1" s="1" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="E1" s="1" t="s">
-        <x:v>206</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="0">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A3" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C3" s="0">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A4" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C4" s="0">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A5" s="0">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C5" s="0">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A6" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C6" s="0">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A7" s="0">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C7" s="0">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A8" s="0">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C8" s="0">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A9" s="0">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C9" s="0">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A10" s="0">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C10" s="0">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A11" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C11" s="0">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A12" s="0">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C12" s="0">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A13" s="0">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C13" s="0">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A14" s="0">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C14" s="0">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E14" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A15" s="0">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B15" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C15" s="0">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D15" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E15" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A16" s="0">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B16" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C16" s="0">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D16" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E16" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A17" s="0">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B17" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C17" s="0">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D17" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A18" s="0">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B18" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C18" s="0">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D18" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E18" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A19" s="0">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B19" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C19" s="0">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D19" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E19" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A20" s="0">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B20" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C20" s="0">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D20" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E20" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A21" s="0">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B21" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C21" s="0">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D21" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E21" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A22" s="0">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C22" s="0">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D22" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E22" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A23" s="0">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B23" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C23" s="0">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D23" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E23" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A24" s="0">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C24" s="0">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D24" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E24" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A25" s="0">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C25" s="0">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D25" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E25" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A26" s="0">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B26" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C26" s="0">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D26" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E26" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A27" s="0">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C27" s="0">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D27" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E27" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A28" s="0">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C28" s="0">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D28" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E28" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A29" s="0">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C29" s="0">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D29" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E29" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A30" s="0">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C30" s="0">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="D30" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E30" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A31" s="0">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C31" s="0">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D31" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E31" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A32" s="0">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C32" s="0">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D32" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E32" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A33" s="0">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C33" s="0">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D33" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E33" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A34" s="0">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C34" s="0">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="D34" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E34" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A35" s="0">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C35" s="0">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D35" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E35" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A36" s="0">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C36" s="0">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D36" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E36" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A37" s="0">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C37" s="0">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D37" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E37" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A38" s="0">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="C38" s="0">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D38" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E38" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A39" s="0">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C39" s="0">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D39" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E39" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A40" s="0">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="C40" s="0">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D40" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E40" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A41" s="0">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="C41" s="0">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D41" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E41" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A42" s="0">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C42" s="0">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D42" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E42" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A43" s="0">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C43" s="0">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D43" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E43" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A44" s="0">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C44" s="0">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D44" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E44" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A45" s="0">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C45" s="0">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D45" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E45" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A46" s="0">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C46" s="0">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D46" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E46" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A47" s="0">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C47" s="0">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D47" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E47" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A48" s="0">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C48" s="0">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D48" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E48" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A49" s="0">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C49" s="0">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D49" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E49" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A50" s="0">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C50" s="0">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D50" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E50" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A51" s="0">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="C51" s="0">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D51" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E51" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A52" s="0">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C52" s="0">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="D52" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E52" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A53" s="0">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="C53" s="0">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D53" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E53" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A54" s="0">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="C54" s="0">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D54" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E54" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A55" s="0">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="B55" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C55" s="0">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D55" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E55" s="0" t="s">
-        <x:v>112</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A56" s="0">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="B56" s="0" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="C56" s="0">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D56" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E56" s="0" t="s">
-        <x:v>114</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A57" s="0">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="B57" s="0" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="C57" s="0">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D57" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E57" s="0" t="s">
-        <x:v>116</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A58" s="0">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="B58" s="0" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="C58" s="0">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="D58" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E58" s="0" t="s">
-        <x:v>118</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A59" s="0">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="B59" s="0" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="C59" s="0">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D59" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E59" s="0" t="s">
-        <x:v>120</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A60" s="0">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="B60" s="0" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="C60" s="0">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D60" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E60" s="0" t="s">
-        <x:v>122</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A61" s="0">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B61" s="0" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="C61" s="0">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D61" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E61" s="0" t="s">
-        <x:v>124</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A62" s="0">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="B62" s="0" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="C62" s="0">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D62" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E62" s="0" t="s">
-        <x:v>126</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A63" s="0">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="B63" s="0" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="C63" s="0">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D63" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E63" s="0" t="s">
-        <x:v>128</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A64" s="0">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="B64" s="0" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="C64" s="0">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D64" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E64" s="0" t="s">
-        <x:v>130</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A65" s="0">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="B65" s="0" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="C65" s="0">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="D65" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E65" s="0" t="s">
-        <x:v>132</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A66" s="0">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="B66" s="0" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="C66" s="0">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D66" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E66" s="0" t="s">
-        <x:v>134</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A67" s="0">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="B67" s="0" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="C67" s="0">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D67" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E67" s="0" t="s">
-        <x:v>136</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A68" s="0">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="B68" s="0" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="C68" s="0">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D68" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E68" s="0" t="s">
-        <x:v>138</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A69" s="0">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="B69" s="0" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="C69" s="0">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D69" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E69" s="0" t="s">
-        <x:v>140</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A70" s="0">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="B70" s="0" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="C70" s="0">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D70" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E70" s="0" t="s">
-        <x:v>142</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A71" s="0">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="B71" s="0" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="C71" s="0">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D71" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E71" s="0" t="s">
-        <x:v>144</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A72" s="0">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="B72" s="0" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="C72" s="0">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D72" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E72" s="0" t="s">
-        <x:v>146</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A73" s="0">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B73" s="0" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="C73" s="0">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D73" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E73" s="0" t="s">
-        <x:v>148</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A74" s="0">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="B74" s="0" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="C74" s="0">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D74" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E74" s="0" t="s">
-        <x:v>150</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A75" s="0">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="B75" s="0" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="C75" s="0">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D75" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E75" s="0" t="s">
-        <x:v>152</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A76" s="0">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="B76" s="0" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="C76" s="0">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D76" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E76" s="0" t="s">
-        <x:v>154</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A77" s="0">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="B77" s="0" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="C77" s="0">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D77" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E77" s="0" t="s">
-        <x:v>156</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A78" s="0">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="B78" s="0" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="C78" s="0">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D78" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E78" s="0" t="s">
-        <x:v>158</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A79" s="0">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="B79" s="0" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="C79" s="0">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D79" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E79" s="0" t="s">
-        <x:v>160</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A80" s="0">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="B80" s="0" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="C80" s="0">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D80" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E80" s="0" t="s">
-        <x:v>162</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A81" s="0">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="B81" s="0" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="C81" s="0">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D81" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E81" s="0" t="s">
-        <x:v>164</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A82" s="0">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="B82" s="0" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="C82" s="0">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="D82" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E82" s="0" t="s">
-        <x:v>166</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A83" s="0">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="B83" s="0" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="C83" s="0">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D83" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E83" s="0" t="s">
-        <x:v>168</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A84" s="0">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="B84" s="0" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="C84" s="0">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D84" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E84" s="0" t="s">
-        <x:v>170</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A85" s="0">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="B85" s="0" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="C85" s="0">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D85" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E85" s="0" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A86" s="0">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="B86" s="0" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="C86" s="0">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D86" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E86" s="0" t="s">
-        <x:v>174</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A87" s="0">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="B87" s="0" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="C87" s="0">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D87" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E87" s="0" t="s">
-        <x:v>176</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A88" s="0">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B88" s="0" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="C88" s="0">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D88" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E88" s="0" t="s">
-        <x:v>178</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A89" s="0">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="B89" s="0" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="C89" s="0">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D89" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E89" s="0" t="s">
-        <x:v>180</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A90" s="0">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="B90" s="0" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="C90" s="0">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D90" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E90" s="0" t="s">
-        <x:v>182</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A91" s="0">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="B91" s="0" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="C91" s="0">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D91" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E91" s="0" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A92" s="0">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="B92" s="0" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="C92" s="0">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D92" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E92" s="0" t="s">
-        <x:v>186</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A93" s="0">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="B93" s="0" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="C93" s="0">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D93" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E93" s="0" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A94" s="0">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="B94" s="0" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="C94" s="0">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D94" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E94" s="0" t="s">
-        <x:v>190</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A95" s="0">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="B95" s="0" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="C95" s="0">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D95" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E95" s="0" t="s">
-        <x:v>192</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A96" s="0">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="B96" s="0" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="C96" s="0">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D96" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E96" s="0" t="s">
-        <x:v>194</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A97" s="0">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="B97" s="0" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="C97" s="0">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D97" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E97" s="0" t="s">
-        <x:v>196</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A98" s="0">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="B98" s="0" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="C98" s="0">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D98" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E98" s="0" t="s">
-        <x:v>198</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A99" s="0">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="B99" s="0" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="C99" s="0">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D99" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E99" s="0" t="s">
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A100" s="0">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="B100" s="0" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="C100" s="0">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D100" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E100" s="0" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A101" s="0">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="B101" s="0" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="C101" s="0">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D101" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E101" s="0" t="s">
-        <x:v>204</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
+  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>99</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>58</v>
+      </c>
+      <c r="D3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>38</v>
+      </c>
+      <c r="D4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>98</v>
+      </c>
+      <c r="D5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>64</v>
+      </c>
+      <c r="D6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9">
+        <v>64</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11">
+        <v>63</v>
+      </c>
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12">
+        <v>95</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13">
+        <v>90</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14">
+        <v>51</v>
+      </c>
+      <c r="D14" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15">
+        <v>82</v>
+      </c>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16">
+        <v>88</v>
+      </c>
+      <c r="D16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17">
+        <v>34</v>
+      </c>
+      <c r="D17" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18">
+        <v>79</v>
+      </c>
+      <c r="D18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19">
+        <v>84</v>
+      </c>
+      <c r="D19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20">
+        <v>51</v>
+      </c>
+      <c r="D20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21">
+        <v>40</v>
+      </c>
+      <c r="D21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22">
+        <v>48</v>
+      </c>
+      <c r="D22" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23">
+        <v>49</v>
+      </c>
+      <c r="D23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24">
+        <v>82</v>
+      </c>
+      <c r="D24" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25">
+        <v>83</v>
+      </c>
+      <c r="D25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26">
+        <v>71</v>
+      </c>
+      <c r="D26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27">
+        <v>91</v>
+      </c>
+      <c r="D27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28">
+        <v>88</v>
+      </c>
+      <c r="D28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29">
+        <v>81</v>
+      </c>
+      <c r="D29" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30">
+        <v>87</v>
+      </c>
+      <c r="D30" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31">
+        <v>26</v>
+      </c>
+      <c r="D31" t="s">
+        <v>4</v>
+      </c>
+      <c r="E31" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32">
+        <v>45</v>
+      </c>
+      <c r="D32" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33">
+        <v>66</v>
+      </c>
+      <c r="D33" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34">
+        <v>67</v>
+      </c>
+      <c r="D34" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35">
+        <v>94</v>
+      </c>
+      <c r="D35" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36">
+        <v>43</v>
+      </c>
+      <c r="D36" t="s">
+        <v>4</v>
+      </c>
+      <c r="E36" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>75</v>
+      </c>
+      <c r="C37">
+        <v>71</v>
+      </c>
+      <c r="D37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38">
+        <v>32</v>
+      </c>
+      <c r="D38" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39">
+        <v>99</v>
+      </c>
+      <c r="D39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E39" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40">
+        <v>64</v>
+      </c>
+      <c r="D40" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>83</v>
+      </c>
+      <c r="C41">
+        <v>60</v>
+      </c>
+      <c r="D41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>85</v>
+      </c>
+      <c r="C42">
+        <v>69</v>
+      </c>
+      <c r="D42" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43">
+        <v>46</v>
+      </c>
+      <c r="D43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>89</v>
+      </c>
+      <c r="C44">
+        <v>81</v>
+      </c>
+      <c r="D44" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>91</v>
+      </c>
+      <c r="C45">
+        <v>80</v>
+      </c>
+      <c r="D45" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>93</v>
+      </c>
+      <c r="C46">
+        <v>51</v>
+      </c>
+      <c r="D46" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>95</v>
+      </c>
+      <c r="C47">
+        <v>65</v>
+      </c>
+      <c r="D47" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>97</v>
+      </c>
+      <c r="C48">
+        <v>36</v>
+      </c>
+      <c r="D48" t="s">
+        <v>15</v>
+      </c>
+      <c r="E48" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>99</v>
+      </c>
+      <c r="C49">
+        <v>31</v>
+      </c>
+      <c r="D49" t="s">
+        <v>15</v>
+      </c>
+      <c r="E49" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>101</v>
+      </c>
+      <c r="C50">
+        <v>58</v>
+      </c>
+      <c r="D50" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>103</v>
+      </c>
+      <c r="C51">
+        <v>30</v>
+      </c>
+      <c r="D51" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>105</v>
+      </c>
+      <c r="C52">
+        <v>75</v>
+      </c>
+      <c r="D52" t="s">
+        <v>15</v>
+      </c>
+      <c r="E52" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>107</v>
+      </c>
+      <c r="C53">
+        <v>45</v>
+      </c>
+      <c r="D53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>109</v>
+      </c>
+      <c r="C54">
+        <v>43</v>
+      </c>
+      <c r="D54" t="s">
+        <v>15</v>
+      </c>
+      <c r="E54" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>111</v>
+      </c>
+      <c r="C55">
+        <v>44</v>
+      </c>
+      <c r="D55" t="s">
+        <v>4</v>
+      </c>
+      <c r="E55" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>113</v>
+      </c>
+      <c r="C56">
+        <v>52</v>
+      </c>
+      <c r="D56" t="s">
+        <v>4</v>
+      </c>
+      <c r="E56" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>115</v>
+      </c>
+      <c r="C57">
+        <v>100</v>
+      </c>
+      <c r="D57" t="s">
+        <v>4</v>
+      </c>
+      <c r="E57" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>117</v>
+      </c>
+      <c r="C58">
+        <v>59</v>
+      </c>
+      <c r="D58" t="s">
+        <v>4</v>
+      </c>
+      <c r="E58" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>119</v>
+      </c>
+      <c r="C59">
+        <v>40</v>
+      </c>
+      <c r="D59" t="s">
+        <v>15</v>
+      </c>
+      <c r="E59" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>121</v>
+      </c>
+      <c r="C60">
+        <v>53</v>
+      </c>
+      <c r="D60" t="s">
+        <v>4</v>
+      </c>
+      <c r="E60" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>123</v>
+      </c>
+      <c r="C61">
+        <v>31</v>
+      </c>
+      <c r="D61" t="s">
+        <v>15</v>
+      </c>
+      <c r="E61" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>125</v>
+      </c>
+      <c r="C62">
+        <v>63</v>
+      </c>
+      <c r="D62" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>127</v>
+      </c>
+      <c r="C63">
+        <v>34</v>
+      </c>
+      <c r="D63" t="s">
+        <v>4</v>
+      </c>
+      <c r="E63" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>129</v>
+      </c>
+      <c r="C64">
+        <v>65</v>
+      </c>
+      <c r="D64" t="s">
+        <v>15</v>
+      </c>
+      <c r="E64" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>131</v>
+      </c>
+      <c r="C65">
+        <v>67</v>
+      </c>
+      <c r="D65" t="s">
+        <v>15</v>
+      </c>
+      <c r="E65" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>133</v>
+      </c>
+      <c r="C66">
+        <v>35</v>
+      </c>
+      <c r="D66" t="s">
+        <v>15</v>
+      </c>
+      <c r="E66" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>135</v>
+      </c>
+      <c r="C67">
+        <v>81</v>
+      </c>
+      <c r="D67" t="s">
+        <v>4</v>
+      </c>
+      <c r="E67" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>137</v>
+      </c>
+      <c r="C68">
+        <v>30</v>
+      </c>
+      <c r="D68" t="s">
+        <v>15</v>
+      </c>
+      <c r="E68" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>139</v>
+      </c>
+      <c r="C69">
+        <v>92</v>
+      </c>
+      <c r="D69" t="s">
+        <v>15</v>
+      </c>
+      <c r="E69" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>141</v>
+      </c>
+      <c r="C70">
+        <v>37</v>
+      </c>
+      <c r="D70" t="s">
+        <v>4</v>
+      </c>
+      <c r="E70" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>143</v>
+      </c>
+      <c r="C71">
+        <v>43</v>
+      </c>
+      <c r="D71" t="s">
+        <v>4</v>
+      </c>
+      <c r="E71" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>145</v>
+      </c>
+      <c r="C72">
+        <v>41</v>
+      </c>
+      <c r="D72" t="s">
+        <v>4</v>
+      </c>
+      <c r="E72" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>147</v>
+      </c>
+      <c r="C73">
+        <v>45</v>
+      </c>
+      <c r="D73" t="s">
+        <v>4</v>
+      </c>
+      <c r="E73" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>149</v>
+      </c>
+      <c r="C74">
+        <v>92</v>
+      </c>
+      <c r="D74" t="s">
+        <v>15</v>
+      </c>
+      <c r="E74" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>151</v>
+      </c>
+      <c r="C75">
+        <v>24</v>
+      </c>
+      <c r="D75" t="s">
+        <v>4</v>
+      </c>
+      <c r="E75" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>153</v>
+      </c>
+      <c r="C76">
+        <v>44</v>
+      </c>
+      <c r="D76" t="s">
+        <v>4</v>
+      </c>
+      <c r="E76" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>155</v>
+      </c>
+      <c r="C77">
+        <v>22</v>
+      </c>
+      <c r="D77" t="s">
+        <v>15</v>
+      </c>
+      <c r="E77" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>157</v>
+      </c>
+      <c r="C78">
+        <v>96</v>
+      </c>
+      <c r="D78" t="s">
+        <v>15</v>
+      </c>
+      <c r="E78" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>159</v>
+      </c>
+      <c r="C79">
+        <v>71</v>
+      </c>
+      <c r="D79" t="s">
+        <v>4</v>
+      </c>
+      <c r="E79" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>161</v>
+      </c>
+      <c r="C80">
+        <v>39</v>
+      </c>
+      <c r="D80" t="s">
+        <v>4</v>
+      </c>
+      <c r="E80" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>163</v>
+      </c>
+      <c r="C81">
+        <v>26</v>
+      </c>
+      <c r="D81" t="s">
+        <v>15</v>
+      </c>
+      <c r="E81" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>165</v>
+      </c>
+      <c r="C82">
+        <v>67</v>
+      </c>
+      <c r="D82" t="s">
+        <v>4</v>
+      </c>
+      <c r="E82" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>167</v>
+      </c>
+      <c r="C83">
+        <v>100</v>
+      </c>
+      <c r="D83" t="s">
+        <v>15</v>
+      </c>
+      <c r="E83" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>169</v>
+      </c>
+      <c r="C84">
+        <v>43</v>
+      </c>
+      <c r="D84" t="s">
+        <v>15</v>
+      </c>
+      <c r="E84" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>171</v>
+      </c>
+      <c r="C85">
+        <v>90</v>
+      </c>
+      <c r="D85" t="s">
+        <v>4</v>
+      </c>
+      <c r="E85" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>173</v>
+      </c>
+      <c r="C86">
+        <v>49</v>
+      </c>
+      <c r="D86" t="s">
+        <v>4</v>
+      </c>
+      <c r="E86" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>175</v>
+      </c>
+      <c r="C87">
+        <v>47</v>
+      </c>
+      <c r="D87" t="s">
+        <v>15</v>
+      </c>
+      <c r="E87" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>177</v>
+      </c>
+      <c r="C88">
+        <v>82</v>
+      </c>
+      <c r="D88" t="s">
+        <v>15</v>
+      </c>
+      <c r="E88" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>179</v>
+      </c>
+      <c r="C89">
+        <v>95</v>
+      </c>
+      <c r="D89" t="s">
+        <v>15</v>
+      </c>
+      <c r="E89" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>181</v>
+      </c>
+      <c r="C90">
+        <v>47</v>
+      </c>
+      <c r="D90" t="s">
+        <v>15</v>
+      </c>
+      <c r="E90" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>183</v>
+      </c>
+      <c r="C91">
+        <v>47</v>
+      </c>
+      <c r="D91" t="s">
+        <v>15</v>
+      </c>
+      <c r="E91" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>185</v>
+      </c>
+      <c r="C92">
+        <v>70</v>
+      </c>
+      <c r="D92" t="s">
+        <v>15</v>
+      </c>
+      <c r="E92" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>187</v>
+      </c>
+      <c r="C93">
+        <v>81</v>
+      </c>
+      <c r="D93" t="s">
+        <v>4</v>
+      </c>
+      <c r="E93" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>189</v>
+      </c>
+      <c r="C94">
+        <v>94</v>
+      </c>
+      <c r="D94" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>191</v>
+      </c>
+      <c r="C95">
+        <v>57</v>
+      </c>
+      <c r="D95" t="s">
+        <v>15</v>
+      </c>
+      <c r="E95" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>193</v>
+      </c>
+      <c r="C96">
+        <v>82</v>
+      </c>
+      <c r="D96" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>195</v>
+      </c>
+      <c r="C97">
+        <v>33</v>
+      </c>
+      <c r="D97" t="s">
+        <v>15</v>
+      </c>
+      <c r="E97" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>197</v>
+      </c>
+      <c r="C98">
+        <v>99</v>
+      </c>
+      <c r="D98" t="s">
+        <v>4</v>
+      </c>
+      <c r="E98" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>199</v>
+      </c>
+      <c r="C99">
+        <v>54</v>
+      </c>
+      <c r="D99" t="s">
+        <v>15</v>
+      </c>
+      <c r="E99" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>201</v>
+      </c>
+      <c r="C100">
+        <v>69</v>
+      </c>
+      <c r="D100" t="s">
+        <v>4</v>
+      </c>
+      <c r="E100" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>203</v>
+      </c>
+      <c r="C101">
+        <v>46</v>
+      </c>
+      <c r="D101" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" t="s">
+        <v>204</v>
+      </c>
+    </row>
+  </sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VersioningAttributes/outputfile.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VersioningAttributes/outputfile.xlsx
@@ -2236,29 +2236,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:B6"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="13.140625" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="2" max="2" width="14.570312" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <x:col min="2" max="2" width="14.570312" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="B1" s="0" t="s">
+      <x:c r="B1" t="s">
         <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <x:c r="A3" s="0" t="s">
+      <x:c r="A3" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
+      <x:c r="B3" t="s">
         <x:v>209</x:v>
       </x:c>
     </x:row>
@@ -2266,7 +2263,7 @@
       <x:c r="A4" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B4" s="0">
+      <x:c r="B4">
         <x:v>60.8837209302326</x:v>
       </x:c>
     </x:row>
@@ -2274,7 +2271,7 @@
       <x:c r="A5" s="3" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B5" s="0">
+      <x:c r="B5">
         <x:v>61.4912280701754</x:v>
       </x:c>
     </x:row>
@@ -2282,32 +2279,25 @@
       <x:c r="A6" s="3" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="B6" s="0">
+      <x:c r="B6">
         <x:v>61.23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:E101"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="4" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="2" max="2" width="20.285156" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="3" max="3" width="4.425781" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="4" max="4" width="7.570312" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="5" max="5" width="14.855469" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
+    <x:col min="2" max="2" width="20.285156" bestFit="1" customWidth="1"/>
+    <x:col min="3" max="3" width="4.425781" bestFit="1" customWidth="1"/>
+    <x:col min="4" max="4" width="7.570312" bestFit="1" customWidth="1"/>
+    <x:col min="5" max="5" width="14.855469" bestFit="1" customWidth="1"/>
   </x:cols>
   <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -4028,26 +4018,15 @@
       </c>
     </row>
   </sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VersioningAttributes/outputfile.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VersioningAttributes/outputfile.xlsx
@@ -2240,7 +2240,7 @@
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:cols>
     <x:col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <x:col min="2" max="2" width="14.570312" bestFit="1" customWidth="1"/>
+    <x:col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -2289,17 +2289,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:dimension ref="A1:E101"/>
-  <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <x:cols>
-    <x:col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
-    <x:col min="2" max="2" width="20.285156" bestFit="1" customWidth="1"/>
-    <x:col min="3" max="3" width="4.425781" bestFit="1" customWidth="1"/>
-    <x:col min="4" max="4" width="7.570312" bestFit="1" customWidth="1"/>
-    <x:col min="5" max="5" width="14.855469" bestFit="1" customWidth="1"/>
-  </x:cols>
-  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E101"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
@@ -4018,8 +4018,8 @@
       </c>
     </row>
   </sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VersioningAttributes/outputfile.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VersioningAttributes/outputfile.xlsx
@@ -2242,48 +2242,48 @@
     <x:col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
     <x:col min="2" max="2" width="14.570312" bestFit="1" customWidth="1"/>
   </x:cols>
-  <x:sheetData>
-    <x:row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <x:c r="A1" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="B1" t="s">
-        <x:v>210</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <x:c r="A3" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="B3" t="s">
-        <x:v>209</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <x:c r="A4" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B4">
-        <x:v>60.8837209302326</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <x:c r="A5" s="3" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B5">
-        <x:v>61.4912280701754</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <x:c r="A6" s="3" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="B6">
-        <x:v>61.23</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
+  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4">
+        <v>60.883720930232556</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="4">
+        <v>61.491228070175438</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B6" s="4">
+        <v>61.23</v>
+      </c>
+    </row>
+  </sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VersioningAttributes/outputfile.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VersioningAttributes/outputfile.xlsx
@@ -2235,57 +2235,57 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:dimension ref="A1:B6"/>
-  <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <x:cols>
-    <x:col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <x:col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <x:c r="A1" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="B1" t="s">
-        <x:v>210</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <x:c r="A3" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="B3" t="s">
-        <x:v>209</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <x:c r="A4" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B4">
-        <x:v>60.8837209302326</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <x:c r="A5" s="3" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B5">
-        <x:v>61.4912280701754</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <x:c r="A6" s="3" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="B6">
-        <x:v>61.23</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4">
+        <v>60.883720930232556</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="4">
+        <v>61.491228070175438</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B6" s="4">
+        <v>61.23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
